--- a/data/trans_orig/P24F-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2007</t>
+          <t>Población según si le gustaría dejar de fumar en 2007 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32720</t>
+          <t>32165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1050</t>
+          <t>1048</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>17400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36590</t>
+          <t>36869</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91705</t>
+          <t>91704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>127863</t>
+          <t>129246</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54582</t>
+          <t>53744</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80291</t>
+          <t>80355</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>155501</t>
+          <t>153564</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197612</t>
+          <t>197891</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136042</t>
+          <t>135827</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>172701</t>
+          <t>174516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63117</t>
+          <t>62965</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89236</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>209326</t>
+          <t>205065</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>255475</t>
+          <t>252452</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74320</t>
+          <t>73719</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107505</t>
+          <t>106130</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,7%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>20471</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40221</t>
+          <t>40279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100044</t>
+          <t>99997</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138732</t>
+          <t>139525</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,32%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>22608</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>44966</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>21922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42697</t>
+          <t>43098</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48696</t>
+          <t>48005</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>82038</t>
+          <t>79275</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>309974</t>
+          <t>312984</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>366539</t>
+          <t>368782</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>168554</t>
+          <t>170523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>215290</t>
+          <t>216001</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>497091</t>
+          <t>496656</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>569884</t>
+          <t>566443</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>273288</t>
+          <t>269779</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>329712</t>
+          <t>325522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206786</t>
+          <t>206721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>252193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>495318</t>
+          <t>489081</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>563145</t>
+          <t>564318</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>41,32%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>126055</t>
+          <t>127430</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>170538</t>
+          <t>171297</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78307</t>
+          <t>76699</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113233</t>
+          <t>111297</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>211914</t>
+          <t>213332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>271057</t>
+          <t>271689</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>826</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6003</t>
+          <t>6724</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19764</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23048</t>
+          <t>23408</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>55136</t>
+          <t>56332</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>81386</t>
+          <t>83491</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>43,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>32173</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>55152</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93988</t>
+          <t>93081</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>129436</t>
+          <t>126606</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73227</t>
+          <t>72596</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99734</t>
+          <t>101108</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>42286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66540</t>
+          <t>66128</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,97%</t>
+          <t>30,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>122410</t>
+          <t>124424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158724</t>
+          <t>161355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,93%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>23490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45851</t>
+          <t>46053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21204</t>
+          <t>20934</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40977</t>
+          <t>40880</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50483</t>
+          <t>49736</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79014</t>
+          <t>78737</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41959</t>
+          <t>43728</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71914</t>
+          <t>72242</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>35269</t>
+          <t>36319</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>61706</t>
+          <t>62014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>84722</t>
+          <t>85139</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123624</t>
+          <t>123453</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>480607</t>
+          <t>480612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>550754</t>
+          <t>552610</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>39,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>274323</t>
+          <t>276896</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>331182</t>
+          <t>330746</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>775717</t>
+          <t>775211</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>868448</t>
+          <t>864450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>501939</t>
+          <t>505339</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>575240</t>
+          <t>578158</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>330293</t>
+          <t>329135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>389451</t>
+          <t>387586</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>852732</t>
+          <t>851167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>946516</t>
+          <t>944458</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,04%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239529</t>
+          <t>239947</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>302795</t>
+          <t>301805</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>133553</t>
+          <t>131120</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>177637</t>
+          <t>175777</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>386331</t>
+          <t>390450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>459901</t>
+          <t>462901</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2012</t>
+          <t>Población según si le gustaría dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7848</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6222</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1049</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36398</t>
+          <t>37264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63135</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13285</t>
+          <t>13334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30681</t>
+          <t>30978</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>54854</t>
+          <t>55979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>86403</t>
+          <t>87846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>187688</t>
+          <t>188243</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224619</t>
+          <t>224977</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125515</t>
+          <t>125459</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>151752</t>
+          <t>152026</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323245</t>
+          <t>323066</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>368123</t>
+          <t>369393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,47%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>60027</t>
+          <t>59408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90416</t>
+          <t>90838</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26659</t>
+          <t>25285</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>47620</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>92055</t>
+          <t>91793</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130264</t>
+          <t>131610</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>21961</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4241</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17590</t>
+          <t>16122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>14058</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32741</t>
+          <t>33386</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>117708</t>
+          <t>115979</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>162473</t>
+          <t>161038</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79967</t>
+          <t>79879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118741</t>
+          <t>118218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>207016</t>
+          <t>208333</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>267402</t>
+          <t>264299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>503175</t>
+          <t>506517</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>563952</t>
+          <t>565926</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,13%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>359504</t>
+          <t>362147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>410952</t>
+          <t>411643</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>885518</t>
+          <t>880621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>960612</t>
+          <t>959090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,66%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>142444</t>
+          <t>141880</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187119</t>
+          <t>187865</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>121747</t>
+          <t>120776</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>163919</t>
+          <t>164862</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>278249</t>
+          <t>273582</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>343473</t>
+          <t>337784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2209</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4339</t>
+          <t>4362</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16391</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35096</t>
+          <t>34648</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16809</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>37651</t>
+          <t>35093</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>36233</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63381</t>
+          <t>63804</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73360</t>
+          <t>72612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100754</t>
+          <t>100067</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>72203</t>
+          <t>74468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98164</t>
+          <t>98080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155987</t>
+          <t>154981</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190832</t>
+          <t>189608</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>33558</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>59921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15106</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34453</t>
+          <t>32791</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>53169</t>
+          <t>54598</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>84657</t>
+          <t>86791</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13810</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32116</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7647</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22621</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25073</t>
+          <t>24599</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48800</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>185960</t>
+          <t>184363</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>236471</t>
+          <t>239543</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120730</t>
+          <t>120235</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168508</t>
+          <t>168334</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>321454</t>
+          <t>320980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397973</t>
+          <t>390458</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>792698</t>
+          <t>790888</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>863855</t>
+          <t>864964</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>583909</t>
+          <t>578231</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>646047</t>
+          <t>642317</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1394177</t>
+          <t>1391348</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1487479</t>
+          <t>1489846</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>64,29%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>251732</t>
+          <t>252552</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>314328</t>
+          <t>315449</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175560</t>
+          <t>177156</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>227924</t>
+          <t>229306</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440963</t>
+          <t>440957</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>524657</t>
+          <t>525830</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5375,7 +5375,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,69%</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si le gustaría dejar de fumar en 2016</t>
+          <t>Población según si le gustaría dejar de fumar en 2016 (tasa de respuesta: 98,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16226</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7854</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6385</t>
+          <t>6052</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19914</t>
+          <t>19254</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,12 +5831,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18270</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37826</t>
+          <t>37947</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12195</t>
+          <t>13280</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28438</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34256</t>
+          <t>35062</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62429</t>
+          <t>59937</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,12 +5944,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>16,85%</t>
         </is>
       </c>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>106486</t>
+          <t>107209</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>138461</t>
+          <t>136052</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62333</t>
+          <t>63720</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>86345</t>
+          <t>84986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>178781</t>
+          <t>180678</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>216824</t>
+          <t>215067</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>60,47%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51148</t>
+          <t>51653</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80628</t>
+          <t>80410</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26144</t>
+          <t>25500</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47811</t>
+          <t>45586</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83585</t>
+          <t>84614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117259</t>
+          <t>117128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12113</t>
+          <t>12305</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>29541</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,44 +6330,44 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>17047</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10034</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>26649</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17047</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>10619</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>26648</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
           <t>4,06%</t>
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>26694</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50704</t>
+          <t>51235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145236</t>
+          <t>141332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>190924</t>
+          <t>189207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121395</t>
+          <t>121309</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>167711</t>
+          <t>163762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>278216</t>
+          <t>277987</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>340602</t>
+          <t>341228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,54%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>417162</t>
+          <t>419500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>472273</t>
+          <t>473350</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>343309</t>
+          <t>343089</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>394634</t>
+          <t>394729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>778956</t>
+          <t>774409</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>852644</t>
+          <t>852238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>140217</t>
+          <t>141959</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187065</t>
+          <t>189026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107058</t>
+          <t>108082</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>147062</t>
+          <t>146148</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>257122</t>
+          <t>261230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>319833</t>
+          <t>319327</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,03%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10052</t>
+          <t>10912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,47 +6899,47 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2932</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8406</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>0,78%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2932</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>921</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8090</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3061</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14325</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>47894</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11218</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>26660</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>40952</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>67870</t>
+          <t>69704</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60507</t>
+          <t>60994</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86201</t>
+          <t>86410</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65505</t>
+          <t>64715</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>86759</t>
+          <t>84297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>131846</t>
+          <t>133004</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164793</t>
+          <t>165939</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14063</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32121</t>
+          <t>31527</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15957</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33439</t>
+          <t>34110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33926</t>
+          <t>34387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>60751</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23207</t>
+          <t>22831</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>46256</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14871</t>
+          <t>14981</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>33951</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41670</t>
+          <t>43835</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71579</t>
+          <t>73849</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200343</t>
+          <t>200276</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258216</t>
+          <t>257897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>157439</t>
+          <t>158205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205673</t>
+          <t>207216</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372495</t>
+          <t>372676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>446566</t>
+          <t>447687</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,71%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>607659</t>
+          <t>607508</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>680504</t>
+          <t>675839</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,73%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>491617</t>
+          <t>487726</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>547849</t>
+          <t>551101</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,25%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1113671</t>
+          <t>1113144</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1206700</t>
+          <t>1204347</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,42%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>219095</t>
+          <t>220672</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>276293</t>
+          <t>279163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159326</t>
+          <t>161830</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210633</t>
+          <t>210037</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>400538</t>
+          <t>398227</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>474109</t>
+          <t>474628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24F-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P24F-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>12995</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32165</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1048</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10269</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17400</t>
+          <t>16991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91704</t>
+          <t>93220</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>129246</t>
+          <t>129102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53744</t>
+          <t>53858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80355</t>
+          <t>78761</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>153564</t>
+          <t>154953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>197891</t>
+          <t>199416</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>135827</t>
+          <t>134210</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>174516</t>
+          <t>172109</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62965</t>
+          <t>63362</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>89554</t>
+          <t>89359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>205065</t>
+          <t>206835</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>252452</t>
+          <t>253897</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>46,07%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73719</t>
+          <t>73823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>106130</t>
+          <t>109394</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20471</t>
+          <t>20566</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40279</t>
+          <t>40039</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99997</t>
+          <t>100504</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>139525</t>
+          <t>139406</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,29%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22608</t>
+          <t>21749</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>44966</t>
+          <t>44618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21779</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43098</t>
+          <t>42761</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>48005</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>79275</t>
+          <t>82650</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>312984</t>
+          <t>309765</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>368782</t>
+          <t>365952</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>37,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,09%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>170523</t>
+          <t>170569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>216001</t>
+          <t>212882</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>496656</t>
+          <t>497232</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>566443</t>
+          <t>567001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>269779</t>
+          <t>273350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>325522</t>
+          <t>325874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206721</t>
+          <t>207223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>252193</t>
+          <t>253225</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,72%</t>
+          <t>37,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>489081</t>
+          <t>494456</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>564318</t>
+          <t>561457</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,11%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>127430</t>
+          <t>125022</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>171297</t>
+          <t>170443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,82 +1655,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>15,29%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>20,84%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>94563</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>77568</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>113173</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>20,65%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>241872</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>212792</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>269070</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>17,71%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>15,58%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>20,95%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>94563</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76699</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>111297</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>17,25%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>20,31%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>241872</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>213332</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>271689</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>17,71%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>15,62%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,7%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>826</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>19829</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8621</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23408</t>
+          <t>22513</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>55320</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>83491</t>
+          <t>80925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32173</t>
+          <t>32538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55152</t>
+          <t>55258</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>39,83%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>93081</t>
+          <t>94524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>126606</t>
+          <t>131010</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72596</t>
+          <t>72207</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101108</t>
+          <t>101185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42286</t>
+          <t>43000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66128</t>
+          <t>66125</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>124424</t>
+          <t>122139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161355</t>
+          <t>160322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23490</t>
+          <t>24269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46053</t>
+          <t>47424</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>20934</t>
+          <t>21659</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40880</t>
+          <t>40603</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49736</t>
+          <t>49488</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>78737</t>
+          <t>79462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -2439,12 +2439,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>43728</t>
+          <t>42325</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>72242</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2454,12 +2454,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>36319</t>
+          <t>34837</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62014</t>
+          <t>61009</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2509,12 +2509,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>85139</t>
+          <t>85318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123453</t>
+          <t>125985</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2524,12 +2524,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>480612</t>
+          <t>481172</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>552610</t>
+          <t>555753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>276896</t>
+          <t>272821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>330746</t>
+          <t>329354</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>775211</t>
+          <t>775466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>864450</t>
+          <t>866010</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,54%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>505339</t>
+          <t>503800</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>578158</t>
+          <t>577745</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>329135</t>
+          <t>329903</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>387586</t>
+          <t>387843</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>851167</t>
+          <t>854570</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>944458</t>
+          <t>950365</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>239947</t>
+          <t>240708</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>301805</t>
+          <t>300911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131120</t>
+          <t>132167</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175777</t>
+          <t>177644</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>390450</t>
+          <t>387870</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>462901</t>
+          <t>463161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7848</t>
+          <t>7394</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,7 +3279,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>6767</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37264</t>
+          <t>37251</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63686</t>
+          <t>63986</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13334</t>
+          <t>13514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30978</t>
+          <t>31044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55979</t>
+          <t>54770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>87846</t>
+          <t>86318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,23%</t>
         </is>
       </c>
     </row>
@@ -3465,12 +3465,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>188243</t>
+          <t>189061</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>224977</t>
+          <t>225133</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>125459</t>
+          <t>127232</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>152026</t>
+          <t>154230</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>323066</t>
+          <t>323953</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>369393</t>
+          <t>367936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,2%</t>
         </is>
       </c>
     </row>
@@ -3578,12 +3578,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59408</t>
+          <t>60277</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>90838</t>
+          <t>90525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3613,12 +3613,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25285</t>
+          <t>26163</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47620</t>
+          <t>48638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3628,12 +3628,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91793</t>
+          <t>92396</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>131610</t>
+          <t>129667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3663,12 +3663,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -3808,12 +3808,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21961</t>
+          <t>22570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3843,12 +3843,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4147</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16122</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3878,12 +3878,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>14058</t>
+          <t>14447</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>33386</t>
+          <t>32237</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>115979</t>
+          <t>117783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>161038</t>
+          <t>161469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3956,12 +3956,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79879</t>
+          <t>79837</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118218</t>
+          <t>118148</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3971,12 +3971,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>208333</t>
+          <t>208569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>264299</t>
+          <t>270369</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -4034,12 +4034,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>506517</t>
+          <t>506906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>565926</t>
+          <t>564979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,5%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362147</t>
+          <t>361063</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>411643</t>
+          <t>415133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,86%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>880621</t>
+          <t>883717</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>959090</t>
+          <t>957402</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4119,12 +4119,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,44%</t>
         </is>
       </c>
     </row>
@@ -4147,12 +4147,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141880</t>
+          <t>140865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>187865</t>
+          <t>186866</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120776</t>
+          <t>118459</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>164862</t>
+          <t>163895</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>273582</t>
+          <t>274184</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>337784</t>
+          <t>339208</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4232,12 +4232,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,83%</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4392,12 +4392,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>969</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8358</t>
+          <t>9091</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4427,12 +4427,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4362</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17076</t>
+          <t>17358</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4462,12 +4462,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,79%</t>
         </is>
       </c>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15312</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>34648</t>
+          <t>34940</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4505,12 +4505,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16809</t>
+          <t>16139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35093</t>
+          <t>35731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4540,12 +4540,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>36443</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>62740</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72612</t>
+          <t>73970</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100067</t>
+          <t>99705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4638,12 +4638,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74468</t>
+          <t>75566</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98080</t>
+          <t>99230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4653,12 +4653,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4673,12 +4673,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>154981</t>
+          <t>155430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189608</t>
+          <t>191775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -4716,12 +4716,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33558</t>
+          <t>34520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>59921</t>
+          <t>58211</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>36,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4751,12 +4751,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>14778</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32791</t>
+          <t>33247</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4766,12 +4766,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54598</t>
+          <t>53857</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86791</t>
+          <t>85391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4801,12 +4801,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,47%</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4946,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13519</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31840</t>
+          <t>32368</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4961,12 +4961,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22621</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4996,12 +4996,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24599</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47893</t>
+          <t>48870</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5059,12 +5059,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184363</t>
+          <t>182928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>239543</t>
+          <t>242415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5074,12 +5074,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5094,12 +5094,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>120235</t>
+          <t>121677</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>168334</t>
+          <t>167330</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5129,12 +5129,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>320980</t>
+          <t>319722</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>390458</t>
+          <t>391343</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5144,12 +5144,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,89%</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>790888</t>
+          <t>792210</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>864964</t>
+          <t>866787</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5187,12 +5187,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>64,3%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5207,12 +5207,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>578231</t>
+          <t>581987</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>642317</t>
+          <t>644571</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5222,12 +5222,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5242,12 +5242,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1391348</t>
+          <t>1397018</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1489846</t>
+          <t>1496123</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>252552</t>
+          <t>252732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>315449</t>
+          <t>314040</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>177156</t>
+          <t>176116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229306</t>
+          <t>230053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>440957</t>
+          <t>447255</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>525830</t>
+          <t>526019</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -5746,12 +5746,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>874</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7894</t>
+          <t>6997</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6052</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19254</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37947</t>
+          <t>37496</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13280</t>
+          <t>12777</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28844</t>
+          <t>29903</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5909,12 +5909,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>35062</t>
+          <t>34134</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>59923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107209</t>
+          <t>108242</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136052</t>
+          <t>137855</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5987,12 +5987,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63720</t>
+          <t>63150</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>84986</t>
+          <t>85763</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6022,12 +6022,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>64,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>180678</t>
+          <t>175349</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>215067</t>
+          <t>214585</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6057,12 +6057,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -6085,12 +6085,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>52172</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80410</t>
+          <t>78705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6100,12 +6100,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6120,12 +6120,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25500</t>
+          <t>25643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45586</t>
+          <t>46935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6135,12 +6135,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6155,12 +6155,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84614</t>
+          <t>85000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>117128</t>
+          <t>119526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12305</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30319</t>
+          <t>29564</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6330,47 +6330,47 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,73%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>17047</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10182</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>25784</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>1,55%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17047</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>10034</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>26649</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>26694</t>
+          <t>25425</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>51235</t>
+          <t>49952</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6400,12 +6400,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141332</t>
+          <t>142497</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189207</t>
+          <t>190462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6443,12 +6443,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>121309</t>
+          <t>122702</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>163762</t>
+          <t>166699</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6478,12 +6478,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>277987</t>
+          <t>277900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>341228</t>
+          <t>339971</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6513,12 +6513,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -6541,12 +6541,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419500</t>
+          <t>419050</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>473350</t>
+          <t>476726</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,87%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>343089</t>
+          <t>343562</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>394729</t>
+          <t>395599</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>774409</t>
+          <t>776699</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>852238</t>
+          <t>854246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6626,12 +6626,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,94%</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6654,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>141959</t>
+          <t>139092</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189026</t>
+          <t>185438</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6669,12 +6669,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108082</t>
+          <t>107454</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>146148</t>
+          <t>147226</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>261230</t>
+          <t>260466</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>319327</t>
+          <t>321052</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,15%</t>
         </is>
       </c>
     </row>
@@ -6884,12 +6884,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6899,12 +6899,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6919,12 +6919,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>8442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6954,12 +6954,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3032</t>
+          <t>3086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6969,12 +6969,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -6997,12 +6997,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26293</t>
+          <t>25969</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>47769</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7012,12 +7012,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7032,12 +7032,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10869</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26660</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42343</t>
+          <t>43226</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>69704</t>
+          <t>69937</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,25%</t>
         </is>
       </c>
     </row>
@@ -7110,12 +7110,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60994</t>
+          <t>61042</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>86410</t>
+          <t>85633</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7125,12 +7125,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,83%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7145,12 +7145,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>64406</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84297</t>
+          <t>85793</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133004</t>
+          <t>131870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>165939</t>
+          <t>164521</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -7223,12 +7223,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13690</t>
+          <t>13373</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31527</t>
+          <t>31322</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7238,12 +7238,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7258,12 +7258,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15957</t>
+          <t>16590</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34110</t>
+          <t>34041</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7293,12 +7293,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>34387</t>
+          <t>34277</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59214</t>
+          <t>59714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,27%</t>
         </is>
       </c>
     </row>
@@ -7453,12 +7453,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22831</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>46256</t>
+          <t>45496</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7468,12 +7468,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14981</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>34130</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>43835</t>
+          <t>41965</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73849</t>
+          <t>71340</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -7566,12 +7566,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>200276</t>
+          <t>202362</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>257897</t>
+          <t>256475</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7581,12 +7581,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>158205</t>
+          <t>157520</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207216</t>
+          <t>206169</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7636,12 +7636,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>372676</t>
+          <t>375283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>447687</t>
+          <t>451042</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -7679,12 +7679,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>607508</t>
+          <t>608088</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>675839</t>
+          <t>676167</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,68%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7714,12 +7714,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>487726</t>
+          <t>490019</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>551101</t>
+          <t>549791</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7749,12 +7749,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1113144</t>
+          <t>1115506</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1204347</t>
+          <t>1208378</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>54,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>58,42%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -7792,12 +7792,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220672</t>
+          <t>220510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>279163</t>
+          <t>277660</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7827,12 +7827,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>161830</t>
+          <t>161051</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>210037</t>
+          <t>210337</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7862,12 +7862,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>398227</t>
+          <t>394630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>474628</t>
+          <t>472751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
